--- a/Imports/modeles/Ecritures.xlsx
+++ b/Imports/modeles/Ecritures.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -435,7 +435,6 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -456,35 +455,30 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Pièce</t>
+          <t>Compte</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Compte</t>
+          <t>Libellé</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Libellé</t>
+          <t>Débit</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Débit</t>
+          <t>Crédit</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Crédit</t>
+          <t>Anal2</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Anal2</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Let</t>
         </is>

--- a/Imports/modeles/Ecritures.xlsx
+++ b/Imports/modeles/Ecritures.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ecritures" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ecritures" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,36 +423,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Mvt</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Jnl</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Jnl</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Mvt</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Compte</t>
@@ -460,25 +463,40 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Libellé</t>
+          <t>LibelCompte</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Débit</t>
+          <t>Libelle</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Crédit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Anal2</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Anal</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LibelAnal</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Let</t>
         </is>
